--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546895</v>
       </c>
       <c r="B2" t="n">
-        <v>79241</v>
+        <v>79245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>229821</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -779,7 +784,7 @@
         <v>122546897</v>
       </c>
       <c r="B3" t="n">
-        <v>78388</v>
+        <v>78392</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,6 +798,11 @@
       </c>
       <c r="E3" t="n">
         <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>78392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R2" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B3" t="n">
-        <v>78392</v>
+        <v>79245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R3" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>79245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R2" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>78392</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R3" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546897</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>78393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122546895</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546897</v>
       </c>
       <c r="B2" t="n">
-        <v>78393</v>
+        <v>78396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122546895</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B2" t="n">
-        <v>78396</v>
+        <v>79351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R2" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>78498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R3" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B2" t="n">
-        <v>79351</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R2" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B3" t="n">
-        <v>78498</v>
+        <v>79355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R3" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>79355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R2" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B3" t="n">
-        <v>79355</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R3" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31444-2023 artfynd.xlsx
+++ b/artfynd/A 31444-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546895</v>
+        <v>122546897</v>
       </c>
       <c r="B2" t="n">
-        <v>79355</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777552</v>
+        <v>777544</v>
       </c>
       <c r="R2" t="n">
-        <v>7106583</v>
+        <v>7106600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546897</v>
+        <v>122546895</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>79355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777544</v>
+        <v>777552</v>
       </c>
       <c r="R3" t="n">
-        <v>7106600</v>
+        <v>7106583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
